--- a/artfynd/A 689-2026 artfynd.xlsx
+++ b/artfynd/A 689-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130982633</v>
       </c>
       <c r="B2" t="n">
-        <v>91813</v>
+        <v>91814</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 689-2026 artfynd.xlsx
+++ b/artfynd/A 689-2026 artfynd.xlsx
@@ -787,7 +787,7 @@
         <v>131082382</v>
       </c>
       <c r="B3" t="n">
-        <v>58043</v>
+        <v>58045</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 689-2026 artfynd.xlsx
+++ b/artfynd/A 689-2026 artfynd.xlsx
@@ -787,7 +787,7 @@
         <v>131082382</v>
       </c>
       <c r="B3" t="n">
-        <v>58045</v>
+        <v>58046</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 689-2026 artfynd.xlsx
+++ b/artfynd/A 689-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -787,7 +787,7 @@
         <v>131082382</v>
       </c>
       <c r="B3" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,6 +895,1198 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>131498448</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58047</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>A 689, Falerum, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>572829</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6446979</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Gärdserum</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Även sång</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>131498523</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91839</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>A 689, Falerum, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>572851</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6447010</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Gärdserum</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>131498504</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99023</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>A 689, Falerum, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>572851</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6446980</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Gärdserum</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>131498367</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99023</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>A 689, Falerum, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>572753</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6447059</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Gärdserum</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>131498573</v>
+      </c>
+      <c r="B8" t="n">
+        <v>92116</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>658</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>A 689, Falerum, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>572752</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6447092</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Gärdserum</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>131498359</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99023</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>A 689, Falerum, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>572776</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6447053</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Gärdserum</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>131498377</v>
+      </c>
+      <c r="B10" t="n">
+        <v>91818</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>A 689, Falerum, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>572750</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6447034</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Gärdserum</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>131498333</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99023</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>A 689, Falerum, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>572777</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6447060</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Gärdserum</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>131498220</v>
+      </c>
+      <c r="B12" t="n">
+        <v>106144</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>A 689, Falerum, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>572768</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6447064</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Gärdserum</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>131498490</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99023</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>A 689, Falerum, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>572868</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6446983</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Gärdserum</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>131498408</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57076</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>A 689, Falerum, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>572807</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6446987</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Gärdserum</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Stöttes 2 ggr</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 689-2026 artfynd.xlsx
+++ b/artfynd/A 689-2026 artfynd.xlsx
@@ -898,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131498448</v>
+        <v>131498523</v>
       </c>
       <c r="B4" t="n">
-        <v>58047</v>
+        <v>91839</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -909,21 +909,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -931,13 +931,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -945,13 +944,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>572829</v>
+        <v>572851</v>
       </c>
       <c r="R4" t="n">
-        <v>6446979</v>
+        <v>6447010</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -983,17 +982,13 @@
           <t>2026-03-07</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Även sång</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1012,10 +1007,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131498523</v>
+        <v>131498448</v>
       </c>
       <c r="B5" t="n">
-        <v>91839</v>
+        <v>58047</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1023,21 +1018,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1045,12 +1040,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1058,13 +1054,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>572851</v>
+        <v>572829</v>
       </c>
       <c r="R5" t="n">
-        <v>6447010</v>
+        <v>6446979</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1096,13 +1092,17 @@
           <t>2026-03-07</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Även sång</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1333,10 +1333,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131498573</v>
+        <v>131498377</v>
       </c>
       <c r="B8" t="n">
-        <v>92116</v>
+        <v>91818</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1344,31 +1344,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -1379,10 +1379,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>572752</v>
+        <v>572750</v>
       </c>
       <c r="R8" t="n">
-        <v>6447092</v>
+        <v>6447034</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1415,11 +1415,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1553,45 +1548,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131498377</v>
+        <v>131498333</v>
       </c>
       <c r="B10" t="n">
-        <v>91818</v>
+        <v>99023</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1599,10 +1591,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>572750</v>
+        <v>572777</v>
       </c>
       <c r="R10" t="n">
-        <v>6447034</v>
+        <v>6447060</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1662,32 +1654,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131498333</v>
+        <v>131498220</v>
       </c>
       <c r="B11" t="n">
-        <v>99023</v>
+        <v>106144</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1705,10 +1697,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>572777</v>
+        <v>572768</v>
       </c>
       <c r="R11" t="n">
-        <v>6447060</v>
+        <v>6447064</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1768,32 +1760,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131498220</v>
+        <v>131498490</v>
       </c>
       <c r="B12" t="n">
-        <v>106144</v>
+        <v>99023</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1811,10 +1803,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>572768</v>
+        <v>572868</v>
       </c>
       <c r="R12" t="n">
-        <v>6447064</v>
+        <v>6446983</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1874,42 +1866,42 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131498490</v>
+        <v>131498408</v>
       </c>
       <c r="B13" t="n">
-        <v>99023</v>
+        <v>57076</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1917,13 +1909,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>572868</v>
+        <v>572807</v>
       </c>
       <c r="R13" t="n">
-        <v>6446983</v>
+        <v>6446987</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1955,13 +1947,17 @@
           <t>2026-03-07</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Stöttes 2 ggr</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1980,42 +1976,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131498408</v>
+        <v>131498573</v>
       </c>
       <c r="B14" t="n">
-        <v>57076</v>
+        <v>92116</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2023,13 +2022,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>572807</v>
+        <v>572752</v>
       </c>
       <c r="R14" t="n">
-        <v>6446987</v>
+        <v>6447092</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2063,7 +2062,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Stöttes 2 ggr</t>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2072,6 +2071,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 689-2026 artfynd.xlsx
+++ b/artfynd/A 689-2026 artfynd.xlsx
@@ -1333,45 +1333,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131498377</v>
+        <v>131498359</v>
       </c>
       <c r="B8" t="n">
-        <v>91818</v>
+        <v>99023</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1379,10 +1376,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>572750</v>
+        <v>572776</v>
       </c>
       <c r="R8" t="n">
-        <v>6447034</v>
+        <v>6447053</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1442,42 +1439,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131498359</v>
+        <v>131498377</v>
       </c>
       <c r="B9" t="n">
-        <v>99023</v>
+        <v>91818</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1485,10 +1485,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>572776</v>
+        <v>572750</v>
       </c>
       <c r="R9" t="n">
-        <v>6447053</v>
+        <v>6447034</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 689-2026 artfynd.xlsx
+++ b/artfynd/A 689-2026 artfynd.xlsx
@@ -901,7 +901,7 @@
         <v>131498523</v>
       </c>
       <c r="B4" t="n">
-        <v>91839</v>
+        <v>91842</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>131498448</v>
       </c>
       <c r="B5" t="n">
-        <v>58047</v>
+        <v>58050</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>131498504</v>
       </c>
       <c r="B6" t="n">
-        <v>99023</v>
+        <v>99026</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         <v>131498367</v>
       </c>
       <c r="B7" t="n">
-        <v>99023</v>
+        <v>99026</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1333,42 +1333,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131498359</v>
+        <v>131498377</v>
       </c>
       <c r="B8" t="n">
-        <v>99023</v>
+        <v>91821</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1376,10 +1379,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>572776</v>
+        <v>572750</v>
       </c>
       <c r="R8" t="n">
-        <v>6447053</v>
+        <v>6447034</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1439,45 +1442,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131498377</v>
+        <v>131498359</v>
       </c>
       <c r="B9" t="n">
-        <v>91818</v>
+        <v>99026</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1485,10 +1485,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>572750</v>
+        <v>572776</v>
       </c>
       <c r="R9" t="n">
-        <v>6447034</v>
+        <v>6447053</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1551,7 +1551,7 @@
         <v>131498333</v>
       </c>
       <c r="B10" t="n">
-        <v>99023</v>
+        <v>99026</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>131498220</v>
       </c>
       <c r="B11" t="n">
-        <v>106144</v>
+        <v>106148</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>131498490</v>
       </c>
       <c r="B12" t="n">
-        <v>99023</v>
+        <v>99026</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
         <v>131498408</v>
       </c>
       <c r="B13" t="n">
-        <v>57076</v>
+        <v>57079</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>131498573</v>
       </c>
       <c r="B14" t="n">
-        <v>92116</v>
+        <v>92119</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 689-2026 artfynd.xlsx
+++ b/artfynd/A 689-2026 artfynd.xlsx
@@ -901,7 +901,7 @@
         <v>131498523</v>
       </c>
       <c r="B4" t="n">
-        <v>91842</v>
+        <v>91843</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>131498448</v>
       </c>
       <c r="B5" t="n">
-        <v>58050</v>
+        <v>58051</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>131498504</v>
       </c>
       <c r="B6" t="n">
-        <v>99026</v>
+        <v>99027</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         <v>131498367</v>
       </c>
       <c r="B7" t="n">
-        <v>99026</v>
+        <v>99027</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
         <v>131498377</v>
       </c>
       <c r="B8" t="n">
-        <v>91821</v>
+        <v>91822</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         <v>131498359</v>
       </c>
       <c r="B9" t="n">
-        <v>99026</v>
+        <v>99027</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>131498333</v>
       </c>
       <c r="B10" t="n">
-        <v>99026</v>
+        <v>99027</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>131498220</v>
       </c>
       <c r="B11" t="n">
-        <v>106148</v>
+        <v>106153</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>131498490</v>
       </c>
       <c r="B12" t="n">
-        <v>99026</v>
+        <v>99027</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
         <v>131498408</v>
       </c>
       <c r="B13" t="n">
-        <v>57079</v>
+        <v>57080</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>131498573</v>
       </c>
       <c r="B14" t="n">
-        <v>92119</v>
+        <v>92120</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 689-2026 artfynd.xlsx
+++ b/artfynd/A 689-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -898,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131498523</v>
+        <v>131498448</v>
       </c>
       <c r="B4" t="n">
-        <v>91843</v>
+        <v>58051</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -909,21 +909,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -931,12 +931,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -944,13 +945,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>572851</v>
+        <v>572829</v>
       </c>
       <c r="R4" t="n">
-        <v>6447010</v>
+        <v>6446979</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -982,13 +983,17 @@
           <t>2026-03-07</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Även sång</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1007,10 +1012,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131498448</v>
+        <v>131498523</v>
       </c>
       <c r="B5" t="n">
-        <v>58051</v>
+        <v>91843</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1018,21 +1023,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1040,13 +1045,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1054,13 +1058,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>572829</v>
+        <v>572851</v>
       </c>
       <c r="R5" t="n">
-        <v>6446979</v>
+        <v>6447010</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1092,17 +1096,13 @@
           <t>2026-03-07</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Även sång</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -2088,6 +2088,767 @@
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>131594070</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99031</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Brunstmossen, Sm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>572780</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6447022</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Gärdserum</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg, Lena Lundin Johansson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>131595013</v>
+      </c>
+      <c r="B16" t="n">
+        <v>97271</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>53</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Brunstmossen, Sm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>572763</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6447086</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Gärdserum</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg, Lena Lundin Johansson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>131592544</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57084</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Brunstmossen, Sm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>572879</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6447017</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Gärdserum</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg, Lena Lundin Johansson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>131594491</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99031</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Brunstmossen, Sm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>572751</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6447069</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Gärdserum</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg, Lena Lundin Johansson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>131586825</v>
+      </c>
+      <c r="B19" t="n">
+        <v>92124</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>658</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Brunstmossen, Sm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>572747</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6447092</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Gärdserum</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>09:34</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>09:34</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Lena Lundin Johansson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Lena Lundin Johansson, Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>131594580</v>
+      </c>
+      <c r="B20" t="n">
+        <v>8453</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Brunstmossen, Sm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>572747</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6447092</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Gärdserum</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Lena Lundin Johansson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Lena Lundin Johansson, Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>131600264</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57893</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Brunstmossen, Sm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>572747</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6447092</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Gärdserum</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Lena Lundin Johansson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Lena Lundin Johansson, Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 689-2026 artfynd.xlsx
+++ b/artfynd/A 689-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -898,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131498448</v>
+        <v>131498523</v>
       </c>
       <c r="B4" t="n">
-        <v>58051</v>
+        <v>91849</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -909,21 +909,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -931,13 +931,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -945,13 +944,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>572829</v>
+        <v>572851</v>
       </c>
       <c r="R4" t="n">
-        <v>6446979</v>
+        <v>6447010</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -983,17 +982,13 @@
           <t>2026-03-07</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Även sång</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1012,10 +1007,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131498523</v>
+        <v>131498448</v>
       </c>
       <c r="B5" t="n">
-        <v>91843</v>
+        <v>58057</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1023,21 +1018,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1045,12 +1040,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1058,13 +1054,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>572851</v>
+        <v>572829</v>
       </c>
       <c r="R5" t="n">
-        <v>6447010</v>
+        <v>6446979</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1096,13 +1092,17 @@
           <t>2026-03-07</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Även sång</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1124,7 +1124,7 @@
         <v>131498504</v>
       </c>
       <c r="B6" t="n">
-        <v>99027</v>
+        <v>99033</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         <v>131498367</v>
       </c>
       <c r="B7" t="n">
-        <v>99027</v>
+        <v>99033</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
         <v>131498377</v>
       </c>
       <c r="B8" t="n">
-        <v>91822</v>
+        <v>91828</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         <v>131498359</v>
       </c>
       <c r="B9" t="n">
-        <v>99027</v>
+        <v>99033</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>131498333</v>
       </c>
       <c r="B10" t="n">
-        <v>99027</v>
+        <v>99033</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>131498220</v>
       </c>
       <c r="B11" t="n">
-        <v>106153</v>
+        <v>106159</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>131498490</v>
       </c>
       <c r="B12" t="n">
-        <v>99027</v>
+        <v>99033</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
         <v>131498408</v>
       </c>
       <c r="B13" t="n">
-        <v>57080</v>
+        <v>57086</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>131498573</v>
       </c>
       <c r="B14" t="n">
-        <v>92120</v>
+        <v>92126</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>131594070</v>
       </c>
       <c r="B15" t="n">
-        <v>99031</v>
+        <v>99033</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>131595013</v>
       </c>
       <c r="B16" t="n">
-        <v>97271</v>
+        <v>97273</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2293,42 +2293,41 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131592544</v>
+        <v>131586825</v>
       </c>
       <c r="B17" t="n">
-        <v>57084</v>
+        <v>92126</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2336,10 +2335,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>572879</v>
+        <v>572747</v>
       </c>
       <c r="R17" t="n">
-        <v>6447017</v>
+        <v>6447092</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2369,83 +2368,93 @@
           <t>2026-03-12</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>09:34</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-03-12</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>09:34</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Lena Lundin Johansson</t>
+          <t>Lena Lundin Johansson, Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131594491</v>
+        <v>131592544</v>
       </c>
       <c r="B18" t="n">
-        <v>99031</v>
+        <v>57086</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Brunstmossen, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>572751</v>
+        <v>572879</v>
       </c>
       <c r="R18" t="n">
-        <v>6447069</v>
+        <v>6447017</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2504,41 +2513,43 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131586825</v>
+        <v>131594580</v>
       </c>
       <c r="B19" t="n">
-        <v>92124</v>
+        <v>8453</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2581,7 +2592,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2591,7 +2602,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2619,54 +2630,54 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131594580</v>
+        <v>131594491</v>
       </c>
       <c r="B20" t="n">
-        <v>8453</v>
+        <v>99033</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Brunstmossen, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>572747</v>
+        <v>572751</v>
       </c>
       <c r="R20" t="n">
-        <v>6447092</v>
+        <v>6447069</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2696,40 +2707,29 @@
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>11:08</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>11:08</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson, Emma Nordenberg</t>
+          <t>Emma Nordenberg, Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2739,7 +2739,7 @@
         <v>131600264</v>
       </c>
       <c r="B21" t="n">
-        <v>57893</v>
+        <v>57895</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2848,6 +2848,107 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>131629003</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79260</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Brunstmossen, Sm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>572795</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6447042</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Gärdserum</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg, Lena Lundin Johansson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 689-2026 artfynd.xlsx
+++ b/artfynd/A 689-2026 artfynd.xlsx
@@ -898,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131498523</v>
+        <v>131498448</v>
       </c>
       <c r="B4" t="n">
-        <v>91849</v>
+        <v>58057</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -909,21 +909,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -931,12 +931,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -944,13 +945,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>572851</v>
+        <v>572829</v>
       </c>
       <c r="R4" t="n">
-        <v>6447010</v>
+        <v>6446979</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -982,13 +983,17 @@
           <t>2026-03-07</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Även sång</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1007,10 +1012,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131498448</v>
+        <v>131498523</v>
       </c>
       <c r="B5" t="n">
-        <v>58057</v>
+        <v>91849</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1018,21 +1023,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1040,13 +1045,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1054,13 +1058,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>572829</v>
+        <v>572851</v>
       </c>
       <c r="R5" t="n">
-        <v>6446979</v>
+        <v>6447010</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1092,17 +1096,13 @@
           <t>2026-03-07</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Även sång</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -2196,45 +2196,54 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131595013</v>
+        <v>131594580</v>
       </c>
       <c r="B16" t="n">
-        <v>97273</v>
+        <v>8453</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>53</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Brunstmossen, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>572763</v>
+        <v>572747</v>
       </c>
       <c r="R16" t="n">
-        <v>6447086</v>
+        <v>6447092</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2264,29 +2273,40 @@
           <t>2026-03-12</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-03-12</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Lena Lundin Johansson</t>
+          <t>Lena Lundin Johansson, Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2408,53 +2428,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131592544</v>
+        <v>131595013</v>
       </c>
       <c r="B18" t="n">
-        <v>57086</v>
+        <v>97273</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>53</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Brunstmossen, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>572879</v>
+        <v>572763</v>
       </c>
       <c r="R18" t="n">
-        <v>6447017</v>
+        <v>6447086</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2513,10 +2525,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131594580</v>
+        <v>131592544</v>
       </c>
       <c r="B19" t="n">
-        <v>8453</v>
+        <v>57086</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2524,30 +2536,29 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2557,10 +2568,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>572747</v>
+        <v>572879</v>
       </c>
       <c r="R19" t="n">
-        <v>6447092</v>
+        <v>6447017</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2590,40 +2601,29 @@
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>11:08</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>11:08</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson, Emma Nordenberg</t>
+          <t>Emma Nordenberg, Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>

--- a/artfynd/A 689-2026 artfynd.xlsx
+++ b/artfynd/A 689-2026 artfynd.xlsx
@@ -898,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131498448</v>
+        <v>131498523</v>
       </c>
       <c r="B4" t="n">
-        <v>58057</v>
+        <v>91849</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -909,21 +909,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -931,13 +931,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -945,13 +944,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>572829</v>
+        <v>572851</v>
       </c>
       <c r="R4" t="n">
-        <v>6446979</v>
+        <v>6447010</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -983,17 +982,13 @@
           <t>2026-03-07</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Även sång</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1012,10 +1007,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131498523</v>
+        <v>131498448</v>
       </c>
       <c r="B5" t="n">
-        <v>91849</v>
+        <v>58057</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1023,21 +1018,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1045,12 +1040,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1058,13 +1054,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>572851</v>
+        <v>572829</v>
       </c>
       <c r="R5" t="n">
-        <v>6447010</v>
+        <v>6446979</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1096,13 +1092,17 @@
           <t>2026-03-07</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Även sång</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 689-2026 artfynd.xlsx
+++ b/artfynd/A 689-2026 artfynd.xlsx
@@ -1124,7 +1124,7 @@
         <v>131498504</v>
       </c>
       <c r="B6" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         <v>131498367</v>
       </c>
       <c r="B7" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         <v>131498359</v>
       </c>
       <c r="B9" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>131498333</v>
       </c>
       <c r="B10" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>131498220</v>
       </c>
       <c r="B11" t="n">
-        <v>106159</v>
+        <v>106160</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>131498490</v>
       </c>
       <c r="B12" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>131498573</v>
       </c>
       <c r="B14" t="n">
-        <v>92126</v>
+        <v>92127</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>131594070</v>
       </c>
       <c r="B15" t="n">
-        <v>99033</v>
+        <v>99034</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2196,54 +2196,54 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131594580</v>
+        <v>131594491</v>
       </c>
       <c r="B16" t="n">
-        <v>8453</v>
+        <v>99034</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Brunstmossen, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>572747</v>
+        <v>572751</v>
       </c>
       <c r="R16" t="n">
-        <v>6447092</v>
+        <v>6447069</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2273,40 +2273,29 @@
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>11:08</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>11:08</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson, Emma Nordenberg</t>
+          <t>Emma Nordenberg, Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2316,7 +2305,7 @@
         <v>131586825</v>
       </c>
       <c r="B17" t="n">
-        <v>92126</v>
+        <v>92127</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2431,7 +2420,7 @@
         <v>131595013</v>
       </c>
       <c r="B18" t="n">
-        <v>97273</v>
+        <v>97274</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2630,54 +2619,54 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131594491</v>
+        <v>131594580</v>
       </c>
       <c r="B20" t="n">
-        <v>99033</v>
+        <v>8453</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Brunstmossen, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>572751</v>
+        <v>572747</v>
       </c>
       <c r="R20" t="n">
-        <v>6447069</v>
+        <v>6447092</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2707,29 +2696,40 @@
           <t>2026-03-12</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-03-12</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Lena Lundin Johansson</t>
+          <t>Lena Lundin Johansson, Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>

--- a/artfynd/A 689-2026 artfynd.xlsx
+++ b/artfynd/A 689-2026 artfynd.xlsx
@@ -901,7 +901,7 @@
         <v>131498523</v>
       </c>
       <c r="B4" t="n">
-        <v>91849</v>
+        <v>91850</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>131498448</v>
       </c>
       <c r="B5" t="n">
-        <v>58057</v>
+        <v>58058</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>131498504</v>
       </c>
       <c r="B6" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         <v>131498367</v>
       </c>
       <c r="B7" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
         <v>131498377</v>
       </c>
       <c r="B8" t="n">
-        <v>91828</v>
+        <v>91829</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         <v>131498359</v>
       </c>
       <c r="B9" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>131498333</v>
       </c>
       <c r="B10" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>131498220</v>
       </c>
       <c r="B11" t="n">
-        <v>106160</v>
+        <v>106161</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>131498490</v>
       </c>
       <c r="B12" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
         <v>131498408</v>
       </c>
       <c r="B13" t="n">
-        <v>57086</v>
+        <v>57087</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>131498573</v>
       </c>
       <c r="B14" t="n">
-        <v>92127</v>
+        <v>92128</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>131594070</v>
       </c>
       <c r="B15" t="n">
-        <v>99034</v>
+        <v>99035</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2196,54 +2196,54 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131594491</v>
+        <v>131594580</v>
       </c>
       <c r="B16" t="n">
-        <v>99034</v>
+        <v>8454</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Brunstmossen, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>572751</v>
+        <v>572747</v>
       </c>
       <c r="R16" t="n">
-        <v>6447069</v>
+        <v>6447092</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2273,81 +2273,94 @@
           <t>2026-03-12</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-03-12</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Lena Lundin Johansson</t>
+          <t>Lena Lundin Johansson, Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131586825</v>
+        <v>131594491</v>
       </c>
       <c r="B17" t="n">
-        <v>92127</v>
+        <v>99035</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Brunstmossen, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>572747</v>
+        <v>572751</v>
       </c>
       <c r="R17" t="n">
-        <v>6447092</v>
+        <v>6447069</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2377,50 +2390,39 @@
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>09:34</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>09:34</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson, Emma Nordenberg</t>
+          <t>Emma Nordenberg, Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131595013</v>
+        <v>131586825</v>
       </c>
       <c r="B18" t="n">
-        <v>97274</v>
+        <v>92128</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2428,34 +2430,41 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>53</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Brunstmossen, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>572763</v>
+        <v>572747</v>
       </c>
       <c r="R18" t="n">
-        <v>6447086</v>
+        <v>6447092</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2485,82 +2494,85 @@
           <t>2026-03-12</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>09:34</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-03-12</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>09:34</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Lena Lundin Johansson</t>
+          <t>Lena Lundin Johansson, Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131592544</v>
+        <v>131595013</v>
       </c>
       <c r="B19" t="n">
-        <v>57086</v>
+        <v>97275</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>53</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Brunstmossen, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>572879</v>
+        <v>572763</v>
       </c>
       <c r="R19" t="n">
-        <v>6447017</v>
+        <v>6447086</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2619,10 +2631,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131594580</v>
+        <v>131592544</v>
       </c>
       <c r="B20" t="n">
-        <v>8453</v>
+        <v>57087</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2630,30 +2642,29 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2663,10 +2674,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>572747</v>
+        <v>572879</v>
       </c>
       <c r="R20" t="n">
-        <v>6447092</v>
+        <v>6447017</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2696,40 +2707,29 @@
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>11:08</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>11:08</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson, Emma Nordenberg</t>
+          <t>Emma Nordenberg, Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2739,7 +2739,7 @@
         <v>131600264</v>
       </c>
       <c r="B21" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2854,7 +2854,7 @@
         <v>131629003</v>
       </c>
       <c r="B22" t="n">
-        <v>79260</v>
+        <v>79261</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 689-2026 artfynd.xlsx
+++ b/artfynd/A 689-2026 artfynd.xlsx
@@ -898,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131498523</v>
+        <v>131498448</v>
       </c>
       <c r="B4" t="n">
-        <v>91850</v>
+        <v>58061</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -909,21 +909,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -931,12 +931,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -944,13 +945,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>572851</v>
+        <v>572829</v>
       </c>
       <c r="R4" t="n">
-        <v>6447010</v>
+        <v>6446979</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -982,13 +983,17 @@
           <t>2026-03-07</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Även sång</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1007,10 +1012,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131498448</v>
+        <v>131498523</v>
       </c>
       <c r="B5" t="n">
-        <v>58058</v>
+        <v>91853</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1018,21 +1023,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1040,13 +1045,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1054,13 +1058,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>572829</v>
+        <v>572851</v>
       </c>
       <c r="R5" t="n">
-        <v>6446979</v>
+        <v>6447010</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1092,17 +1096,13 @@
           <t>2026-03-07</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Även sång</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1124,7 +1124,7 @@
         <v>131498504</v>
       </c>
       <c r="B6" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         <v>131498367</v>
       </c>
       <c r="B7" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
         <v>131498377</v>
       </c>
       <c r="B8" t="n">
-        <v>91829</v>
+        <v>91832</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         <v>131498359</v>
       </c>
       <c r="B9" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>131498333</v>
       </c>
       <c r="B10" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>131498220</v>
       </c>
       <c r="B11" t="n">
-        <v>106161</v>
+        <v>106159</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>131498490</v>
       </c>
       <c r="B12" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
         <v>131498408</v>
       </c>
       <c r="B13" t="n">
-        <v>57087</v>
+        <v>57090</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>131498573</v>
       </c>
       <c r="B14" t="n">
-        <v>92128</v>
+        <v>92131</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>131594070</v>
       </c>
       <c r="B15" t="n">
-        <v>99035</v>
+        <v>99038</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2196,43 +2196,41 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131594580</v>
+        <v>131586825</v>
       </c>
       <c r="B16" t="n">
-        <v>8454</v>
+        <v>92131</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2275,7 +2273,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2285,7 +2283,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2313,54 +2311,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131594491</v>
+        <v>131595013</v>
       </c>
       <c r="B17" t="n">
-        <v>99035</v>
+        <v>97278</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Brunstmossen, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>572751</v>
+        <v>572763</v>
       </c>
       <c r="R17" t="n">
-        <v>6447069</v>
+        <v>6447086</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2412,48 +2401,49 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Lena Lundin Johansson</t>
+          <t>Lena Lundin Johansson, Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131586825</v>
+        <v>131592544</v>
       </c>
       <c r="B18" t="n">
-        <v>92128</v>
+        <v>57090</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2461,10 +2451,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>572747</v>
+        <v>572879</v>
       </c>
       <c r="R18" t="n">
-        <v>6447092</v>
+        <v>6447017</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2494,85 +2484,83 @@
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>09:34</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>09:34</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson, Emma Nordenberg</t>
+          <t>Emma Nordenberg, Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131595013</v>
+        <v>131594580</v>
       </c>
       <c r="B19" t="n">
-        <v>97275</v>
+        <v>8454</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>53</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Brunstmossen, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>572763</v>
+        <v>572747</v>
       </c>
       <c r="R19" t="n">
-        <v>6447086</v>
+        <v>6447092</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2602,82 +2590,94 @@
           <t>2026-03-12</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-03-12</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Lena Lundin Johansson</t>
+          <t>Lena Lundin Johansson, Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131592544</v>
+        <v>131594491</v>
       </c>
       <c r="B20" t="n">
-        <v>57087</v>
+        <v>99038</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Brunstmossen, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>572879</v>
+        <v>572751</v>
       </c>
       <c r="R20" t="n">
-        <v>6447017</v>
+        <v>6447069</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2739,7 +2739,7 @@
         <v>131600264</v>
       </c>
       <c r="B21" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2854,7 +2854,7 @@
         <v>131629003</v>
       </c>
       <c r="B22" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 689-2026 artfynd.xlsx
+++ b/artfynd/A 689-2026 artfynd.xlsx
@@ -1657,7 +1657,7 @@
         <v>131498220</v>
       </c>
       <c r="B11" t="n">
-        <v>106159</v>
+        <v>106160</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2196,52 +2196,54 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131586825</v>
+        <v>131594491</v>
       </c>
       <c r="B16" t="n">
-        <v>92131</v>
+        <v>99038</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Brunstmossen, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>572747</v>
+        <v>572751</v>
       </c>
       <c r="R16" t="n">
-        <v>6447092</v>
+        <v>6447069</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2271,50 +2273,39 @@
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>09:34</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>09:34</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson, Emma Nordenberg</t>
+          <t>Emma Nordenberg, Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131595013</v>
+        <v>131586825</v>
       </c>
       <c r="B17" t="n">
-        <v>97278</v>
+        <v>92131</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2322,34 +2313,41 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>53</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Brunstmossen, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>572763</v>
+        <v>572747</v>
       </c>
       <c r="R17" t="n">
-        <v>6447086</v>
+        <v>6447092</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2379,24 +2377,35 @@
           <t>2026-03-12</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>09:34</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-03-12</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>09:34</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
@@ -2408,53 +2417,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131592544</v>
+        <v>131595013</v>
       </c>
       <c r="B18" t="n">
-        <v>57090</v>
+        <v>97278</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>53</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Brunstmossen, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>572879</v>
+        <v>572763</v>
       </c>
       <c r="R18" t="n">
-        <v>6447017</v>
+        <v>6447086</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2513,10 +2514,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131594580</v>
+        <v>131592544</v>
       </c>
       <c r="B19" t="n">
-        <v>8454</v>
+        <v>57090</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2524,30 +2525,29 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2557,10 +2557,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>572747</v>
+        <v>572879</v>
       </c>
       <c r="R19" t="n">
-        <v>6447092</v>
+        <v>6447017</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2590,94 +2590,83 @@
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>11:08</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>11:08</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson, Emma Nordenberg</t>
+          <t>Emma Nordenberg, Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131594491</v>
+        <v>131594580</v>
       </c>
       <c r="B20" t="n">
-        <v>99038</v>
+        <v>8454</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Brunstmossen, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>572751</v>
+        <v>572747</v>
       </c>
       <c r="R20" t="n">
-        <v>6447069</v>
+        <v>6447092</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2707,29 +2696,40 @@
           <t>2026-03-12</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-03-12</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Lena Lundin Johansson</t>
+          <t>Lena Lundin Johansson, Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>

--- a/artfynd/A 689-2026 artfynd.xlsx
+++ b/artfynd/A 689-2026 artfynd.xlsx
@@ -898,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131498448</v>
+        <v>131498523</v>
       </c>
       <c r="B4" t="n">
-        <v>58061</v>
+        <v>91853</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -909,21 +909,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -931,13 +931,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -945,13 +944,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>572829</v>
+        <v>572851</v>
       </c>
       <c r="R4" t="n">
-        <v>6446979</v>
+        <v>6447010</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -983,17 +982,13 @@
           <t>2026-03-07</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Även sång</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1012,10 +1007,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131498523</v>
+        <v>131498448</v>
       </c>
       <c r="B5" t="n">
-        <v>91853</v>
+        <v>58061</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1023,21 +1018,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1045,12 +1040,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1058,13 +1054,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>572851</v>
+        <v>572829</v>
       </c>
       <c r="R5" t="n">
-        <v>6447010</v>
+        <v>6446979</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1096,13 +1092,17 @@
           <t>2026-03-07</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Även sång</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -2196,54 +2196,52 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131594491</v>
+        <v>131586825</v>
       </c>
       <c r="B16" t="n">
-        <v>99038</v>
+        <v>92131</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Brunstmossen, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>572751</v>
+        <v>572747</v>
       </c>
       <c r="R16" t="n">
-        <v>6447069</v>
+        <v>6447092</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2273,39 +2271,50 @@
           <t>2026-03-12</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>09:34</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-03-12</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>09:34</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Lena Lundin Johansson</t>
+          <t>Lena Lundin Johansson, Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131586825</v>
+        <v>131595013</v>
       </c>
       <c r="B17" t="n">
-        <v>92131</v>
+        <v>97278</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2313,41 +2322,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>53</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Brunstmossen, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>572747</v>
+        <v>572763</v>
       </c>
       <c r="R17" t="n">
-        <v>6447092</v>
+        <v>6447086</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2377,35 +2379,24 @@
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>09:34</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>09:34</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
@@ -2417,45 +2408,54 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131595013</v>
+        <v>131594580</v>
       </c>
       <c r="B18" t="n">
-        <v>97278</v>
+        <v>8454</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>53</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Brunstmossen, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>572763</v>
+        <v>572747</v>
       </c>
       <c r="R18" t="n">
-        <v>6447086</v>
+        <v>6447092</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2485,29 +2485,40 @@
           <t>2026-03-12</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-03-12</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Lena Lundin Johansson</t>
+          <t>Lena Lundin Johansson, Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2619,54 +2630,54 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131594580</v>
+        <v>131594491</v>
       </c>
       <c r="B20" t="n">
-        <v>8454</v>
+        <v>99038</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Brunstmossen, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>572747</v>
+        <v>572751</v>
       </c>
       <c r="R20" t="n">
-        <v>6447092</v>
+        <v>6447069</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2696,40 +2707,29 @@
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>11:08</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>11:08</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson, Emma Nordenberg</t>
+          <t>Emma Nordenberg, Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>

--- a/artfynd/A 689-2026 artfynd.xlsx
+++ b/artfynd/A 689-2026 artfynd.xlsx
@@ -2196,41 +2196,43 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131586825</v>
+        <v>131594580</v>
       </c>
       <c r="B16" t="n">
-        <v>92131</v>
+        <v>8454</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2273,7 +2275,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2283,7 +2285,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2311,45 +2313,54 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131595013</v>
+        <v>131594491</v>
       </c>
       <c r="B17" t="n">
-        <v>97278</v>
+        <v>99038</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Brunstmossen, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>572763</v>
+        <v>572751</v>
       </c>
       <c r="R17" t="n">
-        <v>6447086</v>
+        <v>6447069</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2401,50 +2412,48 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson, Emma Nordenberg</t>
+          <t>Emma Nordenberg, Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131594580</v>
+        <v>131586825</v>
       </c>
       <c r="B18" t="n">
-        <v>8454</v>
+        <v>92131</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2487,7 +2496,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2497,7 +2506,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2525,53 +2534,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131592544</v>
+        <v>131595013</v>
       </c>
       <c r="B19" t="n">
-        <v>57090</v>
+        <v>97278</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>53</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Brunstmossen, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>572879</v>
+        <v>572763</v>
       </c>
       <c r="R19" t="n">
-        <v>6447017</v>
+        <v>6447086</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2623,61 +2624,60 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Lena Lundin Johansson</t>
+          <t>Lena Lundin Johansson, Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131594491</v>
+        <v>131592544</v>
       </c>
       <c r="B20" t="n">
-        <v>99038</v>
+        <v>57090</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Brunstmossen, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>572751</v>
+        <v>572879</v>
       </c>
       <c r="R20" t="n">
-        <v>6447069</v>
+        <v>6447017</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 689-2026 artfynd.xlsx
+++ b/artfynd/A 689-2026 artfynd.xlsx
@@ -901,7 +901,7 @@
         <v>131498523</v>
       </c>
       <c r="B4" t="n">
-        <v>91853</v>
+        <v>91859</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>131498448</v>
       </c>
       <c r="B5" t="n">
-        <v>58061</v>
+        <v>58063</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1124,7 +1124,7 @@
         <v>131498504</v>
       </c>
       <c r="B6" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         <v>131498367</v>
       </c>
       <c r="B7" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
         <v>131498377</v>
       </c>
       <c r="B8" t="n">
-        <v>91832</v>
+        <v>91838</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         <v>131498359</v>
       </c>
       <c r="B9" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>131498333</v>
       </c>
       <c r="B10" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>131498220</v>
       </c>
       <c r="B11" t="n">
-        <v>106160</v>
+        <v>106166</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>131498490</v>
       </c>
       <c r="B12" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
         <v>131498408</v>
       </c>
       <c r="B13" t="n">
-        <v>57090</v>
+        <v>57092</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>131498573</v>
       </c>
       <c r="B14" t="n">
-        <v>92131</v>
+        <v>92137</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>131594070</v>
       </c>
       <c r="B15" t="n">
-        <v>99038</v>
+        <v>99044</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2196,43 +2196,41 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131594580</v>
+        <v>131586825</v>
       </c>
       <c r="B16" t="n">
-        <v>8454</v>
+        <v>92137</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2275,7 +2273,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2285,7 +2283,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2313,54 +2311,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131594491</v>
+        <v>131595013</v>
       </c>
       <c r="B17" t="n">
-        <v>99038</v>
+        <v>97284</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Brunstmossen, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>572751</v>
+        <v>572763</v>
       </c>
       <c r="R17" t="n">
-        <v>6447069</v>
+        <v>6447086</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2412,48 +2401,50 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Lena Lundin Johansson</t>
+          <t>Lena Lundin Johansson, Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131586825</v>
+        <v>131594580</v>
       </c>
       <c r="B18" t="n">
-        <v>92131</v>
+        <v>8454</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2496,7 +2487,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2506,7 +2497,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2534,45 +2525,53 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131595013</v>
+        <v>131592544</v>
       </c>
       <c r="B19" t="n">
-        <v>97278</v>
+        <v>57092</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>53</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Brunstmossen, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>572763</v>
+        <v>572879</v>
       </c>
       <c r="R19" t="n">
-        <v>6447086</v>
+        <v>6447017</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2624,60 +2623,61 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson, Emma Nordenberg</t>
+          <t>Emma Nordenberg, Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131592544</v>
+        <v>131594491</v>
       </c>
       <c r="B20" t="n">
-        <v>57090</v>
+        <v>99044</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Brunstmossen, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>572879</v>
+        <v>572751</v>
       </c>
       <c r="R20" t="n">
-        <v>6447017</v>
+        <v>6447069</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2739,7 +2739,7 @@
         <v>131600264</v>
       </c>
       <c r="B21" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2854,7 +2854,7 @@
         <v>131629003</v>
       </c>
       <c r="B22" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 689-2026 artfynd.xlsx
+++ b/artfynd/A 689-2026 artfynd.xlsx
@@ -2408,10 +2408,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131594580</v>
+        <v>131592544</v>
       </c>
       <c r="B18" t="n">
-        <v>8454</v>
+        <v>57092</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2419,30 +2419,29 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2452,10 +2451,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>572747</v>
+        <v>572879</v>
       </c>
       <c r="R18" t="n">
-        <v>6447092</v>
+        <v>6447017</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2485,50 +2484,39 @@
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>11:08</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>11:08</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson, Emma Nordenberg</t>
+          <t>Emma Nordenberg, Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131592544</v>
+        <v>131594580</v>
       </c>
       <c r="B19" t="n">
-        <v>57092</v>
+        <v>8454</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2536,29 +2524,30 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2568,10 +2557,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>572879</v>
+        <v>572747</v>
       </c>
       <c r="R19" t="n">
-        <v>6447017</v>
+        <v>6447092</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2601,29 +2590,40 @@
           <t>2026-03-12</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-03-12</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Lena Lundin Johansson</t>
+          <t>Lena Lundin Johansson, Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>

--- a/artfynd/A 689-2026 artfynd.xlsx
+++ b/artfynd/A 689-2026 artfynd.xlsx
@@ -898,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131498523</v>
+        <v>131498448</v>
       </c>
       <c r="B4" t="n">
-        <v>91859</v>
+        <v>58063</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -909,21 +909,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -931,12 +931,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -944,13 +945,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>572851</v>
+        <v>572829</v>
       </c>
       <c r="R4" t="n">
-        <v>6447010</v>
+        <v>6446979</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -982,13 +983,17 @@
           <t>2026-03-07</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Även sång</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1007,10 +1012,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131498448</v>
+        <v>131498523</v>
       </c>
       <c r="B5" t="n">
-        <v>58063</v>
+        <v>91859</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1018,21 +1023,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1040,13 +1045,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1054,13 +1058,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>572829</v>
+        <v>572851</v>
       </c>
       <c r="R5" t="n">
-        <v>6446979</v>
+        <v>6447010</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1092,17 +1096,13 @@
           <t>2026-03-07</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Även sång</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -2408,10 +2408,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131592544</v>
+        <v>131594580</v>
       </c>
       <c r="B18" t="n">
-        <v>57092</v>
+        <v>8454</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2419,29 +2419,30 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2451,10 +2452,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>572879</v>
+        <v>572747</v>
       </c>
       <c r="R18" t="n">
-        <v>6447017</v>
+        <v>6447092</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2484,39 +2485,50 @@
           <t>2026-03-12</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-03-12</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Lena Lundin Johansson</t>
+          <t>Lena Lundin Johansson, Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131594580</v>
+        <v>131592544</v>
       </c>
       <c r="B19" t="n">
-        <v>8454</v>
+        <v>57092</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2524,30 +2536,29 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2557,10 +2568,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>572747</v>
+        <v>572879</v>
       </c>
       <c r="R19" t="n">
-        <v>6447092</v>
+        <v>6447017</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2590,40 +2601,29 @@
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>11:08</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>11:08</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson, Emma Nordenberg</t>
+          <t>Emma Nordenberg, Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>

--- a/artfynd/A 689-2026 artfynd.xlsx
+++ b/artfynd/A 689-2026 artfynd.xlsx
@@ -898,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131498448</v>
+        <v>131498523</v>
       </c>
       <c r="B4" t="n">
-        <v>58063</v>
+        <v>91859</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -909,21 +909,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -931,13 +931,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -945,13 +944,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>572829</v>
+        <v>572851</v>
       </c>
       <c r="R4" t="n">
-        <v>6446979</v>
+        <v>6447010</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -983,17 +982,13 @@
           <t>2026-03-07</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Även sång</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1012,10 +1007,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131498523</v>
+        <v>131498448</v>
       </c>
       <c r="B5" t="n">
-        <v>91859</v>
+        <v>58063</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1023,21 +1018,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1045,12 +1040,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1058,13 +1054,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>572851</v>
+        <v>572829</v>
       </c>
       <c r="R5" t="n">
-        <v>6447010</v>
+        <v>6446979</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1096,13 +1092,17 @@
           <t>2026-03-07</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Även sång</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -2408,10 +2408,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131594580</v>
+        <v>131592544</v>
       </c>
       <c r="B18" t="n">
-        <v>8454</v>
+        <v>57092</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2419,30 +2419,29 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2452,10 +2451,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>572747</v>
+        <v>572879</v>
       </c>
       <c r="R18" t="n">
-        <v>6447092</v>
+        <v>6447017</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2485,50 +2484,39 @@
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>11:08</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>11:08</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson, Emma Nordenberg</t>
+          <t>Emma Nordenberg, Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131592544</v>
+        <v>131594580</v>
       </c>
       <c r="B19" t="n">
-        <v>57092</v>
+        <v>8454</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2536,29 +2524,30 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2568,10 +2557,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>572879</v>
+        <v>572747</v>
       </c>
       <c r="R19" t="n">
-        <v>6447017</v>
+        <v>6447092</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2601,29 +2590,40 @@
           <t>2026-03-12</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-03-12</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Lena Lundin Johansson</t>
+          <t>Lena Lundin Johansson, Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>

--- a/artfynd/A 689-2026 artfynd.xlsx
+++ b/artfynd/A 689-2026 artfynd.xlsx
@@ -898,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131498523</v>
+        <v>131498448</v>
       </c>
       <c r="B4" t="n">
-        <v>91859</v>
+        <v>58063</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -909,21 +909,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -931,12 +931,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -944,13 +945,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>572851</v>
+        <v>572829</v>
       </c>
       <c r="R4" t="n">
-        <v>6447010</v>
+        <v>6446979</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -982,13 +983,17 @@
           <t>2026-03-07</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Även sång</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1007,10 +1012,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131498448</v>
+        <v>131498523</v>
       </c>
       <c r="B5" t="n">
-        <v>58063</v>
+        <v>91859</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1018,21 +1023,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1040,13 +1045,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1054,13 +1058,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>572829</v>
+        <v>572851</v>
       </c>
       <c r="R5" t="n">
-        <v>6446979</v>
+        <v>6447010</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1092,17 +1096,13 @@
           <t>2026-03-07</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Även sång</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 689-2026 artfynd.xlsx
+++ b/artfynd/A 689-2026 artfynd.xlsx
@@ -2408,10 +2408,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131592544</v>
+        <v>131594580</v>
       </c>
       <c r="B18" t="n">
-        <v>57092</v>
+        <v>8454</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2419,29 +2419,30 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2451,10 +2452,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>572879</v>
+        <v>572747</v>
       </c>
       <c r="R18" t="n">
-        <v>6447017</v>
+        <v>6447092</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2484,39 +2485,50 @@
           <t>2026-03-12</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-03-12</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Lena Lundin Johansson</t>
+          <t>Lena Lundin Johansson, Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131594580</v>
+        <v>131592544</v>
       </c>
       <c r="B19" t="n">
-        <v>8454</v>
+        <v>57092</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2524,30 +2536,29 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2557,10 +2568,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>572747</v>
+        <v>572879</v>
       </c>
       <c r="R19" t="n">
-        <v>6447092</v>
+        <v>6447017</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2590,40 +2601,29 @@
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>11:08</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>11:08</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson, Emma Nordenberg</t>
+          <t>Emma Nordenberg, Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>

--- a/artfynd/A 689-2026 artfynd.xlsx
+++ b/artfynd/A 689-2026 artfynd.xlsx
@@ -898,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131498448</v>
+        <v>131498523</v>
       </c>
       <c r="B4" t="n">
-        <v>58063</v>
+        <v>91862</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -909,21 +909,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -931,13 +931,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -945,13 +944,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>572829</v>
+        <v>572851</v>
       </c>
       <c r="R4" t="n">
-        <v>6446979</v>
+        <v>6447010</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -983,17 +982,13 @@
           <t>2026-03-07</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Även sång</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1012,10 +1007,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131498523</v>
+        <v>131498448</v>
       </c>
       <c r="B5" t="n">
-        <v>91859</v>
+        <v>58066</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1023,21 +1018,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1045,12 +1040,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1058,13 +1054,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>572851</v>
+        <v>572829</v>
       </c>
       <c r="R5" t="n">
-        <v>6447010</v>
+        <v>6446979</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1096,13 +1092,17 @@
           <t>2026-03-07</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Även sång</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1124,7 +1124,7 @@
         <v>131498504</v>
       </c>
       <c r="B6" t="n">
-        <v>99044</v>
+        <v>99047</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         <v>131498367</v>
       </c>
       <c r="B7" t="n">
-        <v>99044</v>
+        <v>99047</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
         <v>131498377</v>
       </c>
       <c r="B8" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         <v>131498359</v>
       </c>
       <c r="B9" t="n">
-        <v>99044</v>
+        <v>99047</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>131498333</v>
       </c>
       <c r="B10" t="n">
-        <v>99044</v>
+        <v>99047</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>131498220</v>
       </c>
       <c r="B11" t="n">
-        <v>106166</v>
+        <v>106170</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>131498490</v>
       </c>
       <c r="B12" t="n">
-        <v>99044</v>
+        <v>99047</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
         <v>131498408</v>
       </c>
       <c r="B13" t="n">
-        <v>57092</v>
+        <v>57095</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>131498573</v>
       </c>
       <c r="B14" t="n">
-        <v>92137</v>
+        <v>92140</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>131594070</v>
       </c>
       <c r="B15" t="n">
-        <v>99044</v>
+        <v>99047</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>131586825</v>
       </c>
       <c r="B16" t="n">
-        <v>92137</v>
+        <v>92140</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>131595013</v>
       </c>
       <c r="B17" t="n">
-        <v>97284</v>
+        <v>97287</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2401,17 +2401,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson, Emma Nordenberg</t>
+          <t>Emma Nordenberg, Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131594580</v>
+        <v>131592544</v>
       </c>
       <c r="B18" t="n">
-        <v>8454</v>
+        <v>57095</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2419,30 +2419,29 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2452,10 +2451,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>572747</v>
+        <v>572879</v>
       </c>
       <c r="R18" t="n">
-        <v>6447092</v>
+        <v>6447017</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2485,93 +2484,83 @@
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>11:08</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>11:08</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson, Emma Nordenberg</t>
+          <t>Emma Nordenberg, Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131592544</v>
+        <v>131594491</v>
       </c>
       <c r="B19" t="n">
-        <v>57092</v>
+        <v>99047</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Brunstmossen, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>572879</v>
+        <v>572751</v>
       </c>
       <c r="R19" t="n">
-        <v>6447017</v>
+        <v>6447069</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2630,54 +2619,54 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131594491</v>
+        <v>131594580</v>
       </c>
       <c r="B20" t="n">
-        <v>99044</v>
+        <v>8455</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Brunstmossen, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>572751</v>
+        <v>572747</v>
       </c>
       <c r="R20" t="n">
-        <v>6447069</v>
+        <v>6447092</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2707,29 +2696,40 @@
           <t>2026-03-12</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-03-12</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Lena Lundin Johansson</t>
+          <t>Lena Lundin Johansson, Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2739,7 +2739,7 @@
         <v>131600264</v>
       </c>
       <c r="B21" t="n">
-        <v>57901</v>
+        <v>57904</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2854,7 +2854,7 @@
         <v>131629003</v>
       </c>
       <c r="B22" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 689-2026 artfynd.xlsx
+++ b/artfynd/A 689-2026 artfynd.xlsx
@@ -898,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131498523</v>
+        <v>131498448</v>
       </c>
       <c r="B4" t="n">
-        <v>91862</v>
+        <v>58071</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -909,21 +909,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -931,12 +931,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -944,13 +945,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>572851</v>
+        <v>572829</v>
       </c>
       <c r="R4" t="n">
-        <v>6447010</v>
+        <v>6446979</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -982,13 +983,17 @@
           <t>2026-03-07</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Även sång</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1007,10 +1012,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131498448</v>
+        <v>131498523</v>
       </c>
       <c r="B5" t="n">
-        <v>58066</v>
+        <v>91867</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1018,21 +1023,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1040,13 +1045,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1054,13 +1058,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>572829</v>
+        <v>572851</v>
       </c>
       <c r="R5" t="n">
-        <v>6446979</v>
+        <v>6447010</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1092,17 +1096,13 @@
           <t>2026-03-07</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Även sång</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1124,7 +1124,7 @@
         <v>131498504</v>
       </c>
       <c r="B6" t="n">
-        <v>99047</v>
+        <v>99052</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         <v>131498367</v>
       </c>
       <c r="B7" t="n">
-        <v>99047</v>
+        <v>99052</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
         <v>131498377</v>
       </c>
       <c r="B8" t="n">
-        <v>91841</v>
+        <v>91846</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         <v>131498359</v>
       </c>
       <c r="B9" t="n">
-        <v>99047</v>
+        <v>99052</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>131498333</v>
       </c>
       <c r="B10" t="n">
-        <v>99047</v>
+        <v>99052</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>131498220</v>
       </c>
       <c r="B11" t="n">
-        <v>106170</v>
+        <v>106175</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>131498490</v>
       </c>
       <c r="B12" t="n">
-        <v>99047</v>
+        <v>99052</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
         <v>131498408</v>
       </c>
       <c r="B13" t="n">
-        <v>57095</v>
+        <v>57100</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>131498573</v>
       </c>
       <c r="B14" t="n">
-        <v>92140</v>
+        <v>92145</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>131594070</v>
       </c>
       <c r="B15" t="n">
-        <v>99047</v>
+        <v>99052</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2196,41 +2196,43 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131586825</v>
+        <v>131594580</v>
       </c>
       <c r="B16" t="n">
-        <v>92140</v>
+        <v>8455</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2273,7 +2275,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2283,7 +2285,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2311,10 +2313,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131595013</v>
+        <v>131586825</v>
       </c>
       <c r="B17" t="n">
-        <v>97287</v>
+        <v>92145</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2322,34 +2324,41 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>53</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Brunstmossen, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>572763</v>
+        <v>572747</v>
       </c>
       <c r="R17" t="n">
-        <v>6447086</v>
+        <v>6447092</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2379,82 +2388,85 @@
           <t>2026-03-12</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>09:34</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-03-12</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>09:34</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Lena Lundin Johansson</t>
+          <t>Lena Lundin Johansson, Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131592544</v>
+        <v>131595013</v>
       </c>
       <c r="B18" t="n">
-        <v>57095</v>
+        <v>97292</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>53</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Brunstmossen, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>572879</v>
+        <v>572763</v>
       </c>
       <c r="R18" t="n">
-        <v>6447017</v>
+        <v>6447086</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2513,54 +2525,53 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131594491</v>
+        <v>131592544</v>
       </c>
       <c r="B19" t="n">
-        <v>99047</v>
+        <v>57100</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Brunstmossen, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>572751</v>
+        <v>572879</v>
       </c>
       <c r="R19" t="n">
-        <v>6447069</v>
+        <v>6447017</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2619,54 +2630,54 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131594580</v>
+        <v>131594491</v>
       </c>
       <c r="B20" t="n">
-        <v>8455</v>
+        <v>99052</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Brunstmossen, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>572747</v>
+        <v>572751</v>
       </c>
       <c r="R20" t="n">
-        <v>6447092</v>
+        <v>6447069</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2696,40 +2707,29 @@
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>11:08</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>11:08</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson, Emma Nordenberg</t>
+          <t>Emma Nordenberg, Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2739,7 +2739,7 @@
         <v>131600264</v>
       </c>
       <c r="B21" t="n">
-        <v>57904</v>
+        <v>57909</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2854,7 +2854,7 @@
         <v>131629003</v>
       </c>
       <c r="B22" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 689-2026 artfynd.xlsx
+++ b/artfynd/A 689-2026 artfynd.xlsx
@@ -898,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131498448</v>
+        <v>131498523</v>
       </c>
       <c r="B4" t="n">
-        <v>58071</v>
+        <v>91867</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -909,21 +909,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -931,13 +931,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -945,13 +944,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>572829</v>
+        <v>572851</v>
       </c>
       <c r="R4" t="n">
-        <v>6446979</v>
+        <v>6447010</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -983,17 +982,13 @@
           <t>2026-03-07</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Även sång</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1012,10 +1007,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131498523</v>
+        <v>131498448</v>
       </c>
       <c r="B5" t="n">
-        <v>91867</v>
+        <v>58071</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1023,21 +1018,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1045,12 +1040,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1058,13 +1054,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>572851</v>
+        <v>572829</v>
       </c>
       <c r="R5" t="n">
-        <v>6447010</v>
+        <v>6446979</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1096,13 +1092,17 @@
           <t>2026-03-07</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Även sång</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -2196,43 +2196,41 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131594580</v>
+        <v>131586825</v>
       </c>
       <c r="B16" t="n">
-        <v>8455</v>
+        <v>92145</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2275,7 +2273,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2285,7 +2283,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2313,10 +2311,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131586825</v>
+        <v>131595013</v>
       </c>
       <c r="B17" t="n">
-        <v>92145</v>
+        <v>97292</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2324,41 +2322,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>53</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Brunstmossen, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>572747</v>
+        <v>572763</v>
       </c>
       <c r="R17" t="n">
-        <v>6447092</v>
+        <v>6447086</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2388,85 +2379,82 @@
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>09:34</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>09:34</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson, Emma Nordenberg</t>
+          <t>Emma Nordenberg, Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131595013</v>
+        <v>131592544</v>
       </c>
       <c r="B18" t="n">
-        <v>97292</v>
+        <v>57100</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>53</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Brunstmossen, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>572763</v>
+        <v>572879</v>
       </c>
       <c r="R18" t="n">
-        <v>6447086</v>
+        <v>6447017</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2525,10 +2513,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131592544</v>
+        <v>131594580</v>
       </c>
       <c r="B19" t="n">
-        <v>57100</v>
+        <v>8455</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2536,29 +2524,30 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2568,10 +2557,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>572879</v>
+        <v>572747</v>
       </c>
       <c r="R19" t="n">
-        <v>6447017</v>
+        <v>6447092</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2601,29 +2590,40 @@
           <t>2026-03-12</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-03-12</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Lena Lundin Johansson</t>
+          <t>Lena Lundin Johansson, Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>

--- a/artfynd/A 689-2026 artfynd.xlsx
+++ b/artfynd/A 689-2026 artfynd.xlsx
@@ -898,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131498523</v>
+        <v>131498448</v>
       </c>
       <c r="B4" t="n">
-        <v>91867</v>
+        <v>58073</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -909,21 +909,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -931,12 +931,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -944,13 +945,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>572851</v>
+        <v>572829</v>
       </c>
       <c r="R4" t="n">
-        <v>6447010</v>
+        <v>6446979</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -982,13 +983,17 @@
           <t>2026-03-07</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Även sång</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1007,10 +1012,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131498448</v>
+        <v>131498523</v>
       </c>
       <c r="B5" t="n">
-        <v>58071</v>
+        <v>91869</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1018,21 +1023,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1040,13 +1045,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1054,13 +1058,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>572829</v>
+        <v>572851</v>
       </c>
       <c r="R5" t="n">
-        <v>6446979</v>
+        <v>6447010</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1092,17 +1096,13 @@
           <t>2026-03-07</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Även sång</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1124,7 +1124,7 @@
         <v>131498504</v>
       </c>
       <c r="B6" t="n">
-        <v>99052</v>
+        <v>99054</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         <v>131498367</v>
       </c>
       <c r="B7" t="n">
-        <v>99052</v>
+        <v>99054</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
         <v>131498377</v>
       </c>
       <c r="B8" t="n">
-        <v>91846</v>
+        <v>91848</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         <v>131498359</v>
       </c>
       <c r="B9" t="n">
-        <v>99052</v>
+        <v>99054</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>131498333</v>
       </c>
       <c r="B10" t="n">
-        <v>99052</v>
+        <v>99054</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>131498220</v>
       </c>
       <c r="B11" t="n">
-        <v>106175</v>
+        <v>106178</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>131498490</v>
       </c>
       <c r="B12" t="n">
-        <v>99052</v>
+        <v>99054</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
         <v>131498408</v>
       </c>
       <c r="B13" t="n">
-        <v>57100</v>
+        <v>57102</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>131498573</v>
       </c>
       <c r="B14" t="n">
-        <v>92145</v>
+        <v>92147</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>131594070</v>
       </c>
       <c r="B15" t="n">
-        <v>99052</v>
+        <v>99054</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>131586825</v>
       </c>
       <c r="B16" t="n">
-        <v>92145</v>
+        <v>92147</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>131595013</v>
       </c>
       <c r="B17" t="n">
-        <v>97292</v>
+        <v>97294</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
         <v>131592544</v>
       </c>
       <c r="B18" t="n">
-        <v>57100</v>
+        <v>57102</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         <v>131594491</v>
       </c>
       <c r="B20" t="n">
-        <v>99052</v>
+        <v>99054</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2739,7 +2739,7 @@
         <v>131600264</v>
       </c>
       <c r="B21" t="n">
-        <v>57909</v>
+        <v>57911</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2854,7 +2854,7 @@
         <v>131629003</v>
       </c>
       <c r="B22" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 689-2026 artfynd.xlsx
+++ b/artfynd/A 689-2026 artfynd.xlsx
@@ -2408,10 +2408,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131592544</v>
+        <v>131594580</v>
       </c>
       <c r="B18" t="n">
-        <v>57102</v>
+        <v>8455</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2419,29 +2419,30 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2451,10 +2452,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>572879</v>
+        <v>572747</v>
       </c>
       <c r="R18" t="n">
-        <v>6447017</v>
+        <v>6447092</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2484,83 +2485,94 @@
           <t>2026-03-12</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-03-12</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Lena Lundin Johansson</t>
+          <t>Lena Lundin Johansson, Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131594580</v>
+        <v>131594491</v>
       </c>
       <c r="B19" t="n">
-        <v>8455</v>
+        <v>99054</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Brunstmossen, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>572747</v>
+        <v>572751</v>
       </c>
       <c r="R19" t="n">
-        <v>6447092</v>
+        <v>6447069</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2590,94 +2602,82 @@
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>11:08</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>11:08</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson, Emma Nordenberg</t>
+          <t>Emma Nordenberg, Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131594491</v>
+        <v>131592544</v>
       </c>
       <c r="B20" t="n">
-        <v>99054</v>
+        <v>57102</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Brunstmossen, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>572751</v>
+        <v>572879</v>
       </c>
       <c r="R20" t="n">
-        <v>6447069</v>
+        <v>6447017</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 689-2026 artfynd.xlsx
+++ b/artfynd/A 689-2026 artfynd.xlsx
@@ -2408,10 +2408,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131594580</v>
+        <v>131592544</v>
       </c>
       <c r="B18" t="n">
-        <v>8455</v>
+        <v>57102</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2419,30 +2419,29 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2452,10 +2451,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>572747</v>
+        <v>572879</v>
       </c>
       <c r="R18" t="n">
-        <v>6447092</v>
+        <v>6447017</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2485,94 +2484,83 @@
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>11:08</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>11:08</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson, Emma Nordenberg</t>
+          <t>Emma Nordenberg, Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131594491</v>
+        <v>131594580</v>
       </c>
       <c r="B19" t="n">
-        <v>99054</v>
+        <v>8455</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Brunstmossen, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>572751</v>
+        <v>572747</v>
       </c>
       <c r="R19" t="n">
-        <v>6447069</v>
+        <v>6447092</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2602,82 +2590,94 @@
           <t>2026-03-12</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-03-12</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Lena Lundin Johansson</t>
+          <t>Lena Lundin Johansson, Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131592544</v>
+        <v>131594491</v>
       </c>
       <c r="B20" t="n">
-        <v>57102</v>
+        <v>99054</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Brunstmossen, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>572879</v>
+        <v>572751</v>
       </c>
       <c r="R20" t="n">
-        <v>6447017</v>
+        <v>6447069</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 689-2026 artfynd.xlsx
+++ b/artfynd/A 689-2026 artfynd.xlsx
@@ -2196,41 +2196,43 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131586825</v>
+        <v>131594580</v>
       </c>
       <c r="B16" t="n">
-        <v>92147</v>
+        <v>8455</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>106545</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2273,7 +2275,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2283,7 +2285,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2311,45 +2313,54 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131595013</v>
+        <v>131594491</v>
       </c>
       <c r="B17" t="n">
-        <v>97294</v>
+        <v>99054</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Brunstmossen, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>572763</v>
+        <v>572751</v>
       </c>
       <c r="R17" t="n">
-        <v>6447086</v>
+        <v>6447069</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2408,42 +2419,41 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131592544</v>
+        <v>131586825</v>
       </c>
       <c r="B18" t="n">
-        <v>57102</v>
+        <v>92147</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2451,10 +2461,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>572879</v>
+        <v>572747</v>
       </c>
       <c r="R18" t="n">
-        <v>6447017</v>
+        <v>6447092</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2484,83 +2494,85 @@
           <t>2026-03-12</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>09:34</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-03-12</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>09:34</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Lena Lundin Johansson</t>
+          <t>Lena Lundin Johansson, Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131594580</v>
+        <v>131595013</v>
       </c>
       <c r="B19" t="n">
-        <v>8455</v>
+        <v>97294</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>53</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Brunstmossen, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>572747</v>
+        <v>572763</v>
       </c>
       <c r="R19" t="n">
-        <v>6447092</v>
+        <v>6447086</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2590,94 +2602,82 @@
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>11:08</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>11:08</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson, Emma Nordenberg</t>
+          <t>Emma Nordenberg, Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131594491</v>
+        <v>131592544</v>
       </c>
       <c r="B20" t="n">
-        <v>99054</v>
+        <v>57102</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Brunstmossen, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>572751</v>
+        <v>572879</v>
       </c>
       <c r="R20" t="n">
-        <v>6447069</v>
+        <v>6447017</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 689-2026 artfynd.xlsx
+++ b/artfynd/A 689-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130982633</v>
+        <v>131586913</v>
       </c>
       <c r="B2" t="n">
-        <v>91814</v>
+        <v>97435</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,45 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 689, Öjsjön,Falerum, Sm</t>
+          <t>Brunstmossen, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>572747</v>
+        <v>572763</v>
       </c>
       <c r="R2" t="n">
-        <v>6447092</v>
+        <v>6447086</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,29 +754,28 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131082382</v>
+        <v>131930099</v>
       </c>
       <c r="B3" t="n">
-        <v>58047</v>
+        <v>97435</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -795,46 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Öjsjön-Falerum, Sm</t>
+          <t>Brunstmossen, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>572824</v>
+        <v>572809</v>
       </c>
       <c r="R3" t="n">
-        <v>6447033</v>
+        <v>6446972</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,17 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Revirparet i delområde av sitt revir</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,22 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Emma Nordenberg, Elsa Waldo, Lena Lundin Johansson, Magnus Kasselstrand, Stefan Kasselstrand, Mats Oldenborg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131498448</v>
+        <v>131498573</v>
       </c>
       <c r="B4" t="n">
-        <v>58073</v>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -909,35 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -945,13 +915,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>572829</v>
+        <v>572752</v>
       </c>
       <c r="R4" t="n">
-        <v>6446979</v>
+        <v>6447092</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -985,7 +955,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Även sång</t>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -994,6 +964,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1012,10 +983,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131498523</v>
+        <v>131586825</v>
       </c>
       <c r="B5" t="n">
-        <v>91869</v>
+        <v>92245</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1023,45 +994,41 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 689, Falerum, Sm</t>
+          <t>Brunstmossen, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>572851</v>
+        <v>572747</v>
       </c>
       <c r="R5" t="n">
-        <v>6447010</v>
+        <v>6447092</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,12 +1055,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,65 +1086,68 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Lena Lundin Johansson, Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131498504</v>
+        <v>130982633</v>
       </c>
       <c r="B6" t="n">
-        <v>99054</v>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 689, Falerum, Sm</t>
+          <t>A 689, Öjsjön,Falerum, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>572851</v>
+        <v>572747</v>
       </c>
       <c r="R6" t="n">
-        <v>6446980</v>
+        <v>6447092</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,12 +1174,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1227,42 +1207,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131498367</v>
+        <v>131498377</v>
       </c>
       <c r="B7" t="n">
-        <v>99054</v>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1270,10 +1253,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>572753</v>
+        <v>572750</v>
       </c>
       <c r="R7" t="n">
-        <v>6447059</v>
+        <v>6447034</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1333,56 +1316,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131498377</v>
+        <v>131930163</v>
       </c>
       <c r="B8" t="n">
-        <v>91848</v>
+        <v>92370</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>4217</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>A 689, Falerum, Sm</t>
+          <t>Brunstmossen, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>572750</v>
+        <v>572711</v>
       </c>
       <c r="R8" t="n">
-        <v>6447034</v>
+        <v>6447075</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1409,12 +1384,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1430,68 +1410,67 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Emma Nordenberg, Elsa Waldo, Lena Lundin Johansson, Magnus Kasselstrand, Stefan Kasselstrand, Mats Oldenborg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131498359</v>
+        <v>131956817</v>
       </c>
       <c r="B9" t="n">
-        <v>99054</v>
+        <v>92370</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>4217</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 689, Falerum, Sm</t>
+          <t>Brunstmossarna, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>572776</v>
+        <v>572713</v>
       </c>
       <c r="R9" t="n">
-        <v>6447053</v>
+        <v>6447066</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1515,12 +1494,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Högt naturvärde på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1533,57 +1517,75 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Stefan Kasselstrand</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131498333</v>
+        <v>131498595</v>
       </c>
       <c r="B10" t="n">
-        <v>99054</v>
+        <v>92348</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1591,10 +1593,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>572777</v>
+        <v>572721</v>
       </c>
       <c r="R10" t="n">
-        <v>6447060</v>
+        <v>6447101</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1654,42 +1656,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131498220</v>
+        <v>131498523</v>
       </c>
       <c r="B11" t="n">
-        <v>106178</v>
+        <v>91930</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221144</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1697,10 +1702,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>572768</v>
+        <v>572851</v>
       </c>
       <c r="R11" t="n">
-        <v>6447064</v>
+        <v>6447010</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1760,10 +1765,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131498490</v>
+        <v>131629003</v>
       </c>
       <c r="B12" t="n">
-        <v>99054</v>
+        <v>79373</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1771,42 +1776,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>A 689, Falerum, Sm</t>
+          <t>Brunstmossen, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>572868</v>
+        <v>572795</v>
       </c>
       <c r="R12" t="n">
-        <v>6446983</v>
+        <v>6447042</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1833,12 +1833,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1854,22 +1854,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Emma Nordenberg, Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131498408</v>
+        <v>131594089</v>
       </c>
       <c r="B13" t="n">
-        <v>57102</v>
+        <v>57972</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1877,45 +1877,45 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>A 689, Falerum, Sm</t>
+          <t>Brunstmossen, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>572807</v>
+        <v>572809</v>
       </c>
       <c r="R13" t="n">
-        <v>6446987</v>
+        <v>6446972</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1939,17 +1939,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Stöttes 2 ggr</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1964,65 +1959,62 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Emma Nordenberg, Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131498573</v>
+        <v>131594597</v>
       </c>
       <c r="B14" t="n">
-        <v>92147</v>
+        <v>57972</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>A 689, Falerum, Sm</t>
+          <t>Brunstmossen, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>572752</v>
+        <v>572747</v>
       </c>
       <c r="R14" t="n">
         <v>6447092</v>
@@ -2052,17 +2044,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2071,73 +2068,71 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Lena Lundin Johansson, Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131594070</v>
+        <v>131930583</v>
       </c>
       <c r="B15" t="n">
-        <v>99054</v>
+        <v>57972</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Brunstmossen, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>572780</v>
+        <v>572715</v>
       </c>
       <c r="R15" t="n">
-        <v>6447022</v>
+        <v>6447033</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2164,12 +2159,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2189,17 +2184,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Lena Lundin Johansson</t>
+          <t>Emma Nordenberg, Elsa Waldo, Lena Lundin Johansson, Magnus Kasselstrand, Stefan Kasselstrand, Mats Oldenborg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131594580</v>
+        <v>131498408</v>
       </c>
       <c r="B16" t="n">
-        <v>8455</v>
+        <v>57141</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2207,46 +2202,45 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Brunstmossen, Sm</t>
+          <t>A 689, Falerum, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>572747</v>
+        <v>572807</v>
       </c>
       <c r="R16" t="n">
-        <v>6447092</v>
+        <v>6446987</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2270,22 +2264,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>11:08</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>11:08</t>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Stöttes 2 ggr</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2294,73 +2283,71 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson, Emma Nordenberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131594491</v>
+        <v>131592544</v>
       </c>
       <c r="B17" t="n">
-        <v>99054</v>
+        <v>57162</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Brunstmossen, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>572751</v>
+        <v>572879</v>
       </c>
       <c r="R17" t="n">
-        <v>6447069</v>
+        <v>6447017</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2419,41 +2406,42 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131586825</v>
+        <v>131593968</v>
       </c>
       <c r="B18" t="n">
-        <v>92147</v>
+        <v>57162</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2461,10 +2449,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>572747</v>
+        <v>572809</v>
       </c>
       <c r="R18" t="n">
-        <v>6447092</v>
+        <v>6446972</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2494,50 +2482,39 @@
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>09:34</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>09:34</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson</t>
+          <t>Emma Nordenberg</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson, Emma Nordenberg</t>
+          <t>Emma Nordenberg, Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131595013</v>
+        <v>131082382</v>
       </c>
       <c r="B19" t="n">
-        <v>97294</v>
+        <v>58114</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2545,34 +2522,46 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>53</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Brunstmossen, Sm</t>
+          <t>Öjsjön-Falerum, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>572763</v>
+        <v>572824</v>
       </c>
       <c r="R19" t="n">
-        <v>6447086</v>
+        <v>6447033</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2599,12 +2588,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Revirparet i delområde av sitt revir</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2619,68 +2613,72 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Lena Lundin Johansson</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131592544</v>
+        <v>131498448</v>
       </c>
       <c r="B20" t="n">
-        <v>57102</v>
+        <v>58114</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Brunstmossen, Sm</t>
+          <t>A 689, Falerum, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>572879</v>
+        <v>572829</v>
       </c>
       <c r="R20" t="n">
-        <v>6447017</v>
+        <v>6446979</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2704,12 +2702,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Även sång</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2724,52 +2727,53 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Emma Nordenberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Emma Nordenberg, Lena Lundin Johansson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131600264</v>
+        <v>131594580</v>
       </c>
       <c r="B21" t="n">
-        <v>57911</v>
+        <v>8460</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2814,7 +2818,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2824,7 +2828,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2833,6 +2837,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2851,48 +2856,53 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131629003</v>
+        <v>131498333</v>
       </c>
       <c r="B22" t="n">
-        <v>79310</v>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Brunstmossen, Sm</t>
+          <t>A 689, Falerum, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>572795</v>
+        <v>572777</v>
       </c>
       <c r="R22" t="n">
-        <v>6447042</v>
+        <v>6447060</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2919,12 +2929,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2940,15 +2950,1172 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>131498359</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>A 689, Falerum, Sm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>572776</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6447053</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Gärdserum</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>131498367</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>A 689, Falerum, Sm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>572753</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6447059</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Gärdserum</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>131498490</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>A 689, Falerum, Sm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>572868</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6446983</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Gärdserum</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>131498504</v>
+      </c>
+      <c r="B26" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>A 689, Falerum, Sm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>572851</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6446980</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Gärdserum</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>131594070</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Brunstmossen, Sm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>572780</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6447022</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Gärdserum</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
           <t>Emma Nordenberg</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
+      <c r="AX27" t="inlineStr">
         <is>
           <t>Emma Nordenberg, Lena Lundin Johansson</t>
         </is>
       </c>
-      <c r="AY22" t="inlineStr"/>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>131594178</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Brunstmossen, Sm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>572727</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6447035</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Gärdserum</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg, Lena Lundin Johansson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>131594480</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Brunstmossen, Sm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>572751</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6447069</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Gärdserum</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Emma Nordenberg, Lena Lundin Johansson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>131939629</v>
+      </c>
+      <c r="B30" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Öjsjön, Falerum, Sm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>572707</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6447081</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Gärdserum</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand, Lena Lundin Johansson, Elsa Waldo, Emma Nordenberg, Mats Oldenborg</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>131939640</v>
+      </c>
+      <c r="B31" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Öjsjön, Falerum, Sm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>572723</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6447059</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Gärdserum</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Stefan Kasselstrand, Lena Lundin Johansson, Elsa Waldo, Emma Nordenberg, Mats Oldenborg</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>132698673</v>
+      </c>
+      <c r="B32" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>A 689, Falerum, Sm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>572722</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6447098</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Gärdserum</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>131498220</v>
+      </c>
+      <c r="B33" t="n">
+        <v>106243</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>A 689, Falerum, Sm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>572768</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6447064</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Gärdserum</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 689-2026 artfynd.xlsx
+++ b/artfynd/A 689-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AZ33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131586913</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131930099</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -980,6 +995,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131498573</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1095,6 +1115,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131586825</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1204,6 +1229,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130982633</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1313,6 +1343,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131498377</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1419,6 +1454,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131930163</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1544,6 +1584,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131956817</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1653,6 +1698,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131498595</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1762,6 +1812,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131498523</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1863,6 +1918,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131629003</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1968,6 +2028,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131594089</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2083,6 +2148,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131594597</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2188,6 +2258,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131930583</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2298,6 +2373,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131498408</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2403,6 +2483,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131592544</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2508,6 +2593,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131593968</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2622,6 +2712,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131082382</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2736,6 +2831,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131498448</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2853,6 +2953,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131594580</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2959,6 +3064,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131498333</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3065,6 +3175,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131498359</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3171,6 +3286,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131498367</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3277,6 +3397,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131498490</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3383,6 +3508,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131498504</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3489,6 +3619,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131594070</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3586,6 +3721,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131594178</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3692,6 +3832,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131594480</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3798,6 +3943,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131939629</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3904,6 +4054,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131939640</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4010,6 +4165,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132698673</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4116,8 +4276,47 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131498220</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>